--- a/data/trans_camb/P16A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,68</t>
+          <t>1,13; 8,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,66</t>
+          <t>-1,84; 5,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,11</t>
+          <t>-3,62; 2,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 4,08</t>
+          <t>-5,0; 4,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 2,14</t>
+          <t>-6,03; 2,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,25</t>
+          <t>-5,38; 2,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,91</t>
+          <t>-0,17; 5,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,07</t>
+          <t>-2,42; 3,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,78</t>
+          <t>-2,94; 2,08</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 198,1</t>
+          <t>14,84; 187,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 121,5</t>
+          <t>-23,78; 123,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 70,46</t>
+          <t>-48,03; 56,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 61,28</t>
+          <t>-44,59; 62,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 34,66</t>
+          <t>-54,27; 42,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 39,65</t>
+          <t>-46,54; 33,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 97,19</t>
+          <t>-2,48; 97,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 51,44</t>
+          <t>-28,51; 55,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 30,83</t>
+          <t>-34,26; 36,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,37</t>
+          <t>-3,92; 4,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,01</t>
+          <t>-3,5; 4,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,5</t>
+          <t>-2,3; 5,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 6,1</t>
+          <t>-2,73; 5,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,47</t>
+          <t>-2,5; 5,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,64</t>
+          <t>-4,62; 2,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 3,76</t>
+          <t>-2,02; 3,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,86</t>
+          <t>-2,23; 3,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,26</t>
+          <t>-2,16; 3,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 93,83</t>
+          <t>-45,27; 87,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 106,82</t>
+          <t>-39,31; 102,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 115,48</t>
+          <t>-26,93; 119,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 108,02</t>
+          <t>-27,41; 99,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 100,18</t>
+          <t>-27,14; 95,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 50,76</t>
+          <t>-47,65; 47,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 67,84</t>
+          <t>-25,24; 69,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 65,96</t>
+          <t>-24,53; 64,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 55,82</t>
+          <t>-23,98; 57,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,47</t>
+          <t>-2,59; 4,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,22</t>
+          <t>-2,25; 4,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 2,9</t>
+          <t>-7,42; 3,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 2,55</t>
+          <t>-9,27; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 6,21</t>
+          <t>-7,49; 6,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 6,23</t>
+          <t>-6,92; 6,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,15</t>
+          <t>-2,8; 2,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,8</t>
+          <t>-2,61; 3,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,73</t>
+          <t>-7,73; 2,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 72,26</t>
+          <t>-27,52; 65,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 68,8</t>
+          <t>-25,08; 73,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,66; 39,97</t>
+          <t>-73,27; 44,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 37,33</t>
+          <t>-63,98; 55,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,18; 89,11</t>
+          <t>-55,02; 93,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 93,06</t>
+          <t>-45,13; 87,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 47,91</t>
+          <t>-28,55; 39,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 58,8</t>
+          <t>-25,72; 49,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,41; 33,42</t>
+          <t>-69,32; 29,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,44</t>
+          <t>0,8; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,2</t>
+          <t>-1,35; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,67</t>
+          <t>-2,17; 2,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,2</t>
+          <t>0,33; 6,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,33</t>
+          <t>-1,88; 3,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,65</t>
+          <t>-5,41; 0,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,03</t>
+          <t>1,16; 4,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,71</t>
+          <t>-0,84; 2,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,0</t>
+          <t>-3,01; 0,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,66; 90,4</t>
+          <t>9,5; 83,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 52,8</t>
+          <t>-16,66; 54,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 44,46</t>
+          <t>-27,62; 44,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 112,24</t>
+          <t>3,42; 106,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 59,8</t>
+          <t>-22,69; 59,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 8,57</t>
+          <t>-65,94; 9,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,8; 80,7</t>
+          <t>14,44; 79,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 44,59</t>
+          <t>-10,41; 40,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 15,54</t>
+          <t>-38,74; 13,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,21</t>
+          <t>-2,15; 5,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,68</t>
+          <t>-3,9; 2,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 2,73</t>
+          <t>-4,45; 2,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,42</t>
+          <t>-1,52; 4,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,54</t>
+          <t>-0,33; 5,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,41</t>
+          <t>-0,42; 5,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,06</t>
+          <t>-0,56; 3,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,56</t>
+          <t>-1,0; 3,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,7</t>
+          <t>-0,81; 3,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 100,79</t>
+          <t>-23,62; 99,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,1; 54,16</t>
+          <t>-41,22; 51,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 58,37</t>
+          <t>-48,17; 46,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 112,52</t>
+          <t>-19,77; 95,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 140,0</t>
+          <t>-6,08; 128,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 126,12</t>
+          <t>-8,5; 130,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 81,15</t>
+          <t>-8,18; 75,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 73,2</t>
+          <t>-13,46; 64,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 78,25</t>
+          <t>-10,82; 75,04</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,86</t>
+          <t>-0,02; 9,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,51</t>
+          <t>-3,17; 4,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,86; -0,56</t>
+          <t>-7,27; -0,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,55</t>
+          <t>0,44; 4,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,38</t>
+          <t>2,03; 6,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,06</t>
+          <t>-0,47; 3,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,92</t>
+          <t>1,26; 4,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,34</t>
+          <t>1,52; 5,4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,43</t>
+          <t>-1,17; 2,42</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 216,27</t>
+          <t>-5,25; 217,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 123,49</t>
+          <t>-43,84; 118,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-91,53; 19,24</t>
+          <t>-91,87; 22,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,47; 109,6</t>
+          <t>6,53; 101,66</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,47; 150,36</t>
+          <t>31,58; 147,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 95,68</t>
+          <t>-8,79; 92,46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,1; 111,97</t>
+          <t>19,57; 110,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22,11; 117,43</t>
+          <t>23,08; 120,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 54,67</t>
+          <t>-20,89; 54,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,92</t>
+          <t>1,11; 3,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,1</t>
+          <t>-0,45; 2,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,0</t>
+          <t>-2,26; 1,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,25</t>
+          <t>0,6; 3,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,22</t>
+          <t>0,76; 3,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,78</t>
+          <t>-1,09; 1,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,18</t>
+          <t>1,39; 3,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,26</t>
+          <t>0,5; 2,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,08</t>
+          <t>-1,18; 0,99</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,35; 61,27</t>
+          <t>14,62; 62,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 33,02</t>
+          <t>-6,13; 34,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 15,05</t>
+          <t>-31,4; 16,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,87; 57,47</t>
+          <t>8,53; 55,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,32; 54,92</t>
+          <t>10,89; 56,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 30,27</t>
+          <t>-15,92; 30,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,63; 50,97</t>
+          <t>19,43; 51,27</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,55; 36,56</t>
+          <t>7,02; 37,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 17,24</t>
+          <t>-17,19; 15,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 8,93</t>
+          <t>0,79; 8,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,71</t>
+          <t>-1,3; 5,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 2,63</t>
+          <t>-4,14; 2,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,02</t>
+          <t>-4,29; 4,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,63</t>
+          <t>-5,98; 2,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,09</t>
+          <t>-5,22; 1,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,98</t>
+          <t>-0,07; 5,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,35</t>
+          <t>-2,45; 3,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,08</t>
+          <t>-3,54; 1,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,36%</t>
+          <t>-12,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,51%</t>
+          <t>-15,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,14%</t>
+          <t>-12,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,84; 187,92</t>
+          <t>4,69; 177,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 123,95</t>
+          <t>-17,42; 123,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 56,21</t>
+          <t>-49,23; 51,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 62,7</t>
+          <t>-42,13; 75,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 42,72</t>
+          <t>-55,56; 34,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 33,82</t>
+          <t>-45,64; 34,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 97,76</t>
+          <t>-1,61; 98,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 55,9</t>
+          <t>-29,14; 51,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 36,88</t>
+          <t>-39,66; 23,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,18</t>
+          <t>-3,58; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 4,54</t>
+          <t>-2,95; 4,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,57</t>
+          <t>-2,28; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,83</t>
+          <t>-2,63; 5,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,37</t>
+          <t>-3,17; 4,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,56</t>
+          <t>-4,67; 2,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,98</t>
+          <t>-1,63; 3,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,65</t>
+          <t>-1,71; 4,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,26</t>
+          <t>-2,42; 2,82</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-9,97%</t>
+          <t>-16,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 87,29</t>
+          <t>-41,01; 91,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 102,85</t>
+          <t>-37,43; 96,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 119,42</t>
+          <t>-26,17; 116,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 99,42</t>
+          <t>-29,65; 102,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 95,87</t>
+          <t>-34,28; 86,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 47,35</t>
+          <t>-47,05; 38,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 69,19</t>
+          <t>-19,1; 69,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 64,22</t>
+          <t>-20,11; 68,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 57,05</t>
+          <t>-28,31; 47,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>1,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,18</t>
+          <t>-2,14; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,36</t>
+          <t>-2,49; 4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 3,05</t>
+          <t>-1,97; 5,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 2,94</t>
+          <t>-8,58; 3,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 6,61</t>
+          <t>-7,77; 5,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 6,27</t>
+          <t>-5,58; 7,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,7</t>
+          <t>-2,94; 2,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,37</t>
+          <t>-2,63; 3,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,44</t>
+          <t>-1,81; 4,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-22,45%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,31%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 65,23</t>
+          <t>-23,22; 74,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 73,38</t>
+          <t>-26,67; 70,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 44,38</t>
+          <t>-21,04; 81,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 55,45</t>
+          <t>-60,44; 57,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,02; 93,57</t>
+          <t>-55,22; 94,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 87,5</t>
+          <t>-39,22; 103,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 39,56</t>
+          <t>-30,22; 43,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 49,03</t>
+          <t>-27,1; 54,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 29,63</t>
+          <t>-18,69; 65,77</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,47</t>
+          <t>0,72; 5,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,14</t>
+          <t>-1,12; 3,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,71</t>
+          <t>-1,66; 2,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,08</t>
+          <t>0,43; 6,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,36</t>
+          <t>-2,04; 3,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,6</t>
+          <t>-3,37; 1,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,94</t>
+          <t>1,15; 4,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,5</t>
+          <t>-0,9; 2,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,92</t>
+          <t>-1,51; 1,73</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,73%</t>
+          <t>-10,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,47%</t>
+          <t>-0,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,5; 83,63</t>
+          <t>8,77; 90,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 54,26</t>
+          <t>-14,35; 52,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 44,95</t>
+          <t>-21,11; 45,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 106,43</t>
+          <t>4,45; 113,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 59,58</t>
+          <t>-23,94; 59,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 9,69</t>
+          <t>-38,71; 26,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,44; 79,53</t>
+          <t>13,83; 80,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 40,66</t>
+          <t>-11,06; 41,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 13,45</t>
+          <t>-19,94; 27,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>2,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,12</t>
+          <t>-1,52; 5,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,62</t>
+          <t>-3,82; 2,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,42</t>
+          <t>-4,32; 2,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,06</t>
+          <t>-1,53; 4,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,51</t>
+          <t>-0,57; 5,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,75</t>
+          <t>0,97; 6,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,79</t>
+          <t>-0,76; 3,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,36</t>
+          <t>-0,67; 3,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,68</t>
+          <t>-0,22; 4,13</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-12,06%</t>
+          <t>-14,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 99,4</t>
+          <t>-18,25; 95,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 51,06</t>
+          <t>-40,62; 56,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 46,26</t>
+          <t>-47,64; 46,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 95,36</t>
+          <t>-21,73; 103,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 128,53</t>
+          <t>-8,63; 127,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 130,45</t>
+          <t>11,43; 163,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 75,31</t>
+          <t>-10,72; 71,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 64,59</t>
+          <t>-10,19; 73,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 75,04</t>
+          <t>-2,56; 84,84</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-2,77</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 9,18</t>
+          <t>0,23; 9,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,77</t>
+          <t>-2,83; 4,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -0,42</t>
+          <t>-6,2; 1,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,35</t>
+          <t>0,84; 4,69</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,52</t>
+          <t>1,78; 6,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,96</t>
+          <t>-0,42; 3,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,96</t>
+          <t>1,32; 4,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,4</t>
+          <t>1,58; 5,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,42</t>
+          <t>-1,14; 2,67</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-66,14%</t>
+          <t>-48,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 217,83</t>
+          <t>-4,53; 217,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 118,05</t>
+          <t>-38,54; 120,63</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-91,87; 22,94</t>
+          <t>-88,22; 86,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,53; 101,66</t>
+          <t>14,36; 113,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>31,58; 147,47</t>
+          <t>26,75; 146,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 92,46</t>
+          <t>-8,48; 89,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,57; 110,54</t>
+          <t>20,7; 110,5</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>23,08; 120,63</t>
+          <t>25,49; 121,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 54,03</t>
+          <t>-20,8; 58,06</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,93</t>
+          <t>1,06; 3,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,17</t>
+          <t>-0,45; 2,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,02</t>
+          <t>-1,13; 1,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,27</t>
+          <t>0,62; 3,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,21</t>
+          <t>0,71; 3,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,83</t>
+          <t>-0,04; 2,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,18</t>
+          <t>1,31; 3,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,31</t>
+          <t>0,43; 2,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,99</t>
+          <t>-0,28; 1,61</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-6,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,62; 62,6</t>
+          <t>14,37; 61,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 34,73</t>
+          <t>-6,31; 32,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 16,18</t>
+          <t>-15,13; 22,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,53; 55,88</t>
+          <t>8,53; 54,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,89; 56,96</t>
+          <t>10,05; 53,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 30,61</t>
+          <t>-0,45; 39,12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,43; 51,27</t>
+          <t>18,43; 52,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7,02; 37,1</t>
+          <t>6,18; 38,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 15,38</t>
+          <t>-4,2; 25,81</t>
         </is>
       </c>
     </row>
